--- a/artfynd/S 2129-2026 artfynd.xlsx
+++ b/artfynd/S 2129-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135774165</v>
       </c>
       <c r="B2" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135774333</v>
       </c>
       <c r="B3" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 2129-2026 artfynd.xlsx
+++ b/artfynd/S 2129-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135774165</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135774333</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 2129-2026 artfynd.xlsx
+++ b/artfynd/S 2129-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135774165</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135774333</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 2129-2026 artfynd.xlsx
+++ b/artfynd/S 2129-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135774165</v>
       </c>
       <c r="B2" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135774333</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 2129-2026 artfynd.xlsx
+++ b/artfynd/S 2129-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135774165</v>
       </c>
       <c r="B2" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135774333</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 2129-2026 artfynd.xlsx
+++ b/artfynd/S 2129-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135774165</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135774333</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 2129-2026 artfynd.xlsx
+++ b/artfynd/S 2129-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135774165</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135774333</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
